--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_11.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03681062426841279</v>
+        <v>0.02903451532438245</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008464239976449508</v>
+        <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44757910</v>
+        <v>3785210</v>
       </c>
       <c r="L2" t="n">
-        <v>22528272</v>
+        <v>1754751</v>
       </c>
       <c r="M2" t="n">
-        <v>4850922</v>
+        <v>344664</v>
       </c>
       <c r="N2" t="n">
-        <v>148011</v>
+        <v>9437</v>
       </c>
       <c r="O2" t="n">
-        <v>2971784</v>
+        <v>216300</v>
       </c>
       <c r="P2" t="n">
-        <v>1182429</v>
+        <v>87381</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7949241399765015</v>
+        <v>0.7346441745758057</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6166815757751465</v>
+        <v>0.5253850817680359</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5174610614776611</v>
+        <v>0.4034073650836945</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1382507681846619</v>
+        <v>0.09780287742614746</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5753876566886902</v>
+        <v>0.4603959321975708</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6809085607528687</v>
+        <v>0.5582059621810913</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01002384208639214</v>
+        <v>0.007566977503591745</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002029011818888065</v>
+        <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>44757910</v>
+        <v>3785210</v>
       </c>
       <c r="E3" t="n">
-        <v>9744154</v>
+        <v>1123174</v>
       </c>
       <c r="F3" t="n">
-        <v>428712</v>
+        <v>66053</v>
       </c>
       <c r="G3" t="n">
-        <v>33912</v>
+        <v>5191</v>
       </c>
       <c r="H3" t="n">
-        <v>48909</v>
+        <v>8040</v>
       </c>
       <c r="I3" t="n">
-        <v>6057</v>
+        <v>1040</v>
       </c>
       <c r="J3" t="n">
-        <v>110182529</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>113059184</v>
+        <v>10060056</v>
       </c>
       <c r="L3" t="n">
-        <v>129480588</v>
+        <v>11490912</v>
       </c>
       <c r="M3" t="n">
-        <v>164805745</v>
+        <v>14961899</v>
       </c>
       <c r="N3" t="n">
-        <v>177719489</v>
+        <v>16238840</v>
       </c>
       <c r="O3" t="n">
-        <v>171819613</v>
+        <v>15649909</v>
       </c>
       <c r="P3" t="n">
-        <v>176942938</v>
+        <v>16152910</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8134888410568237</v>
+        <v>0.7587546706199646</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6233295202255249</v>
+        <v>0.5253893136978149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4711321294307709</v>
+        <v>0.364962100982666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.15049047768116</v>
+        <v>0.1047310456633568</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5294529795646667</v>
+        <v>0.4219845533370972</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5555104613304138</v>
+        <v>0.4505754709243774</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07875988666966945</v>
+        <v>0.06695375273854839</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03200610849614379</v>
+        <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10557566</v>
+        <v>1228160</v>
       </c>
       <c r="E4" t="n">
-        <v>22528272</v>
+        <v>1754751</v>
       </c>
       <c r="F4" t="n">
-        <v>2460376</v>
+        <v>271626</v>
       </c>
       <c r="G4" t="n">
-        <v>154494</v>
+        <v>20271</v>
       </c>
       <c r="H4" t="n">
-        <v>387047</v>
+        <v>56480</v>
       </c>
       <c r="I4" t="n">
-        <v>54074</v>
+        <v>8618</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>11546720</v>
+        <v>1367230</v>
       </c>
       <c r="L4" t="n">
-        <v>14003177</v>
+        <v>1585182</v>
       </c>
       <c r="M4" t="n">
-        <v>4523546</v>
+        <v>509718</v>
       </c>
       <c r="N4" t="n">
-        <v>922587</v>
+        <v>87053</v>
       </c>
       <c r="O4" t="n">
-        <v>2193054</v>
+        <v>253513</v>
       </c>
       <c r="P4" t="n">
-        <v>554117</v>
+        <v>69158</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999977350234985</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8040993809700012</v>
+        <v>0.7465047836303711</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6199877262115479</v>
+        <v>0.5253872275352478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.493211030960083</v>
+        <v>0.3832229673862457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1441112160682678</v>
+        <v>0.1011484637856483</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5514654517173767</v>
+        <v>0.4403541684150696</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6118505597114563</v>
+        <v>0.498649001121521</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>714949</v>
+        <v>103135</v>
       </c>
       <c r="E5" t="n">
-        <v>3356517</v>
+        <v>342631</v>
       </c>
       <c r="F5" t="n">
-        <v>4850922</v>
+        <v>344664</v>
       </c>
       <c r="G5" t="n">
-        <v>296283</v>
+        <v>27672</v>
       </c>
       <c r="H5" t="n">
-        <v>940565</v>
+        <v>107216</v>
       </c>
       <c r="I5" t="n">
-        <v>137055</v>
+        <v>19062</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10261786</v>
+        <v>1203504</v>
       </c>
       <c r="L5" t="n">
-        <v>13613563</v>
+        <v>1585155</v>
       </c>
       <c r="M5" t="n">
-        <v>5445387</v>
+        <v>599719</v>
       </c>
       <c r="N5" t="n">
-        <v>835513</v>
+        <v>80670</v>
       </c>
       <c r="O5" t="n">
-        <v>2641149</v>
+        <v>296278</v>
       </c>
       <c r="P5" t="n">
-        <v>946116</v>
+        <v>106551</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999982714653015</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8785890936851501</v>
+        <v>0.8434007167816162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8462538719177246</v>
+        <v>0.8068751692771912</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9445015788078308</v>
+        <v>0.9324173331260681</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9902124404907227</v>
+        <v>0.9897829294204712</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9730873107910156</v>
+        <v>0.9665088057518005</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9916480183601379</v>
+        <v>0.9892964959144592</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>180217</v>
+        <v>19497</v>
       </c>
       <c r="E6" t="n">
-        <v>250816</v>
+        <v>25642</v>
       </c>
       <c r="F6" t="n">
-        <v>270618</v>
+        <v>21799</v>
       </c>
       <c r="G6" t="n">
-        <v>148011</v>
+        <v>9437</v>
       </c>
       <c r="H6" t="n">
-        <v>117245</v>
+        <v>11641</v>
       </c>
       <c r="I6" t="n">
-        <v>16546</v>
+        <v>2084</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>86844</v>
+        <v>15256</v>
       </c>
       <c r="E7" t="n">
-        <v>586521</v>
+        <v>83253</v>
       </c>
       <c r="F7" t="n">
-        <v>1231683</v>
+        <v>130844</v>
       </c>
       <c r="G7" t="n">
-        <v>395658</v>
+        <v>28570</v>
       </c>
       <c r="H7" t="n">
-        <v>2971784</v>
+        <v>216300</v>
       </c>
       <c r="I7" t="n">
-        <v>340385</v>
+        <v>38354</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7144</v>
+        <v>1182</v>
       </c>
       <c r="E8" t="n">
-        <v>65169</v>
+        <v>10482</v>
       </c>
       <c r="F8" t="n">
-        <v>132157</v>
+        <v>19396</v>
       </c>
       <c r="G8" t="n">
-        <v>42240</v>
+        <v>5349</v>
       </c>
       <c r="H8" t="n">
-        <v>699288</v>
+        <v>70136</v>
       </c>
       <c r="I8" t="n">
-        <v>1182429</v>
+        <v>87381</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
